--- a/data/planning/mixed.xlsx
+++ b/data/planning/mixed.xlsx
@@ -3243,50 +3243,85 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>work_type_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sla_deadline_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>required_transport_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>service_duration_source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -3316,50 +3351,85 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3389,50 +3459,85 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3462,50 +3567,85 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3535,50 +3675,85 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3608,50 +3783,85 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3681,50 +3891,85 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3754,50 +3999,85 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3827,50 +4107,85 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3900,50 +4215,85 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3973,50 +4323,85 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -4046,50 +4431,85 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4119,50 +4539,85 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4192,50 +4647,85 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -4265,50 +4755,85 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -4338,50 +4863,85 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -4411,50 +4971,85 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -4484,50 +5079,85 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -4557,50 +5187,85 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -4630,50 +5295,85 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -4703,50 +5403,85 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4776,50 +5511,85 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -4849,50 +5619,85 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -4922,50 +5727,85 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -4995,50 +5835,85 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -11661,25 +12536,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>travel_minutes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>documents_minutes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>norm_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -11693,25 +12583,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>synthetic_1900_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11725,25 +12630,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>synthetic_1900_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -11757,25 +12677,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>synthetic_1900_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>

--- a/data/planning/mixed.xlsx
+++ b/data/planning/mixed.xlsx
@@ -3572,85 +3572,120 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>work_type_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sla_deadline_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>required_transport_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>service_duration_source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>lifecycle_state</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>execution_cycle</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>actual_started_at</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>actual_completed_at</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>cancel_reason</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>last_event_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -3680,85 +3715,120 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3788,85 +3858,120 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3896,85 +4001,120 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4004,85 +4144,120 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4112,85 +4287,120 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4220,85 +4430,120 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4328,85 +4573,120 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4436,85 +4716,120 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -4544,85 +4859,120 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4652,85 +5002,120 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -4760,85 +5145,120 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4868,85 +5288,120 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4976,85 +5431,120 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -5084,85 +5574,120 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5192,85 +5717,120 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -5300,85 +5860,120 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -5408,85 +6003,120 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -5516,85 +6146,120 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5624,85 +6289,120 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -5732,85 +6432,120 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -5840,85 +6575,120 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -5948,85 +6718,120 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -6056,85 +6861,120 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -6164,85 +7004,120 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -13498,25 +14373,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>travel_minutes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>documents_minutes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>norm_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -13530,25 +14420,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>synthetic_1900_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13562,25 +14467,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>synthetic_1900_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -13594,25 +14514,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>synthetic_1900_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>

--- a/data/planning/mixed.xlsx
+++ b/data/planning/mixed.xlsx
@@ -30,14 +30,13 @@
     <sheet name="brigades" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="notification_events" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="ticket_appliances" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="ticket_assignments" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ticket_comments" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="work_events" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="worker_day_states" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="brigade_members" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="day_plan_revisions" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="equipment_movements" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="routes" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ticket_comments" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="work_events" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="worker_day_states" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="brigade_members" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="day_plan_revisions" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="equipment_movements" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="routes" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3617,75 +3616,85 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>assigned_worker_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>is_pinned</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>execution_cycle</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>actual_started_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>actual_completed_at</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cancel_reason</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>last_event_id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -3760,52 +3769,52 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -3820,15 +3829,25 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3903,52 +3922,52 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -3963,15 +3982,25 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4046,52 +4075,52 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -4106,15 +4135,25 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4189,52 +4228,52 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -4249,15 +4288,25 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4332,52 +4381,52 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -4392,15 +4441,25 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4475,52 +4534,52 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -4535,15 +4594,25 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4618,52 +4687,52 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4678,15 +4747,25 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4761,52 +4840,52 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4821,15 +4900,25 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -4904,52 +4993,52 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4964,15 +5053,25 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -5047,52 +5146,52 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5107,15 +5206,25 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -5190,52 +5299,52 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5250,15 +5359,25 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -5333,52 +5452,52 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5393,15 +5512,25 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5476,52 +5605,52 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -5536,15 +5665,25 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -5619,52 +5758,52 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -5679,15 +5818,25 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5762,52 +5911,52 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -5822,15 +5971,25 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -5905,52 +6064,52 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -5965,15 +6124,25 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -6048,52 +6217,52 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -6108,15 +6277,25 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -6191,52 +6370,52 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -6251,15 +6430,25 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -6334,52 +6523,52 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -6394,15 +6583,25 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -6477,52 +6676,52 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -6537,15 +6736,25 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -6620,52 +6829,52 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -6680,15 +6889,25 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -6763,52 +6982,52 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -6823,15 +7042,25 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -6906,52 +7135,52 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -6966,15 +7195,25 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -7049,52 +7288,52 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -7109,15 +7348,25 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -12962,12 +13211,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>author_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assigned_at</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -12987,32 +13251,164 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ticket_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>author_id</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>worker_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>route_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>occurred_at</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>recorded_at</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>previous_state</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>new_state</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>before_revision</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>after_revision</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>idempotency_key</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>new_ticket</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2030-01-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>waiting_assignment</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>synthetic-1900-ticket-1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"ticket_id":1}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -13032,77 +13428,77 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>worker_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ticket_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>route_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>revision</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>route_date</t>
+          <t>available</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>occurred_at</t>
+          <t>unavailable_at</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>recorded_at</t>
+          <t>unavailable_until</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>last_location_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>current_ticket_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>current_destination_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>en_route_started_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>expected_available_at</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>previous_state</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>new_state</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>before_revision</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>after_revision</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>idempotency_key</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
@@ -13114,7 +13510,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>new_ticket</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -13124,7 +13520,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2030-01-15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13134,17 +13530,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2030-01-15</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -13164,7 +13560,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>waiting_assignment</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -13174,17 +13570,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>synthetic-1900-ticket-1</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"ticket_id":1}</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -13209,164 +13605,60 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>brigade_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>worker_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>district_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>route_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>revision</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>unavailable_at</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unavailable_until</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>last_location_id</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>current_ticket_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>current_destination_id</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>en_route_started_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>expected_available_at</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2030-01-15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1</t>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -13386,12 +13678,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>brigade_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>route_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>previous_revision</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fingerprint</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>is_current</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -13403,43 +13745,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>2030-01-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>037af78dc92cfa511d01a1148b4013f72d2ef1c959523e157a79e73e128339a2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -13459,22 +13815,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>ticket_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>route_date</t>
+          <t>execution_cycle</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>revision</t>
+          <t>appliance_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>previous_revision</t>
+          <t>office_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -13484,35 +13840,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>movement</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fingerprint</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_current</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -13526,7 +13867,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2030-01-15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13536,7 +13877,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13546,35 +13887,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>consume</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>037af78dc92cfa511d01a1148b4013f72d2ef1c959523e157a79e73e128339a2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13657,113 +13983,6 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ticket_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>execution_cycle</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>appliance_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>office_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>movement</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>consume</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
           <t>worker_id</t>
         </is>
       </c>
